--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_301_R31.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_301_R31.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4004</v>
+        <v>3.0204</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3726</v>
+        <v>3.0934</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0278</v>
+        <v>-0.073</v>
       </c>
       <c r="G2" t="n">
         <v>2.8464</v>
@@ -610,13 +610,13 @@
         <v>0.9278</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7859</v>
+        <v>0.4059</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2636</v>
+        <v>-0.0156</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5223</v>
+        <v>0.4215</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1873</v>
+        <v>2.4807</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7831</v>
+        <v>0.9758</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4042</v>
+        <v>1.505</v>
       </c>
       <c r="G3" t="n">
         <v>2.5711</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0075</v>
+        <v>0.286</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7389</v>
+        <v>-0.5463</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7314000000000001</v>
+        <v>0.8323</v>
       </c>
       <c r="V3" t="n">
         <v>-1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1567</v>
+        <v>1.4165</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6732</v>
+        <v>1.8659</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.4494</v>
       </c>
       <c r="G4" t="n">
         <v>0.4442</v>
@@ -766,13 +766,13 @@
         <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5764</v>
+        <v>-0.3165</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6721</v>
+        <v>-0.4795</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0958</v>
+        <v>0.163</v>
       </c>
       <c r="V4" t="n">
         <v>2.6805</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0791</v>
+        <v>1.3054</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2451</v>
+        <v>2.4377</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.166</v>
+        <v>-1.1324</v>
       </c>
       <c r="G5" t="n">
         <v>2.0518</v>
@@ -844,13 +844,13 @@
         <v>0.6959</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.0602</v>
+        <v>0.1661</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8215</v>
+        <v>-0.6289</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7613</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>-1.6083</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6937</v>
+        <v>1.0715</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3663</v>
+        <v>0.6768</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3274</v>
+        <v>0.3946</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8714</v>
@@ -922,13 +922,13 @@
         <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.203</v>
+        <v>0.1748</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.187</v>
+        <v>-0.8764</v>
       </c>
       <c r="U6" t="n">
-        <v>0.984</v>
+        <v>1.0513</v>
       </c>
       <c r="V6" t="n">
         <v>1.0722</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6163999999999999</v>
+        <v>0.5052</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0981</v>
+        <v>1.8189</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4817</v>
+        <v>-1.3137</v>
       </c>
       <c r="G7" t="n">
         <v>-0.5139</v>
@@ -1000,13 +1000,13 @@
         <v>0.6959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4345</v>
+        <v>0.3233</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1142</v>
+        <v>-0.165</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3203</v>
+        <v>0.4883</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4749</v>
+        <v>0.3405</v>
       </c>
       <c r="E8" t="n">
         <v>-0.5354</v>
       </c>
       <c r="F8" t="n">
-        <v>1.0103</v>
+        <v>0.8759</v>
       </c>
       <c r="G8" t="n">
         <v>-0.2777</v>
@@ -1078,13 +1078,13 @@
         <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4332</v>
+        <v>0.2987</v>
       </c>
       <c r="T8" t="n">
         <v>-0.5149</v>
       </c>
       <c r="U8" t="n">
-        <v>0.948</v>
+        <v>0.8136</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.1408</v>
+        <v>-1.4125</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.057</v>
+        <v>-2.2615</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9162</v>
+        <v>0.849</v>
       </c>
       <c r="G9" t="n">
         <v>0.1514</v>
@@ -1156,13 +1156,13 @@
         <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4938</v>
+        <v>0.2221</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2592</v>
+        <v>-0.4637</v>
       </c>
       <c r="U9" t="n">
-        <v>0.753</v>
+        <v>0.6858</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3943</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0732</v>
+        <v>-1.897</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5309</v>
+        <v>-3.2203</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4577</v>
+        <v>1.3232</v>
       </c>
       <c r="G10" t="n">
         <v>-1.7408</v>
@@ -1234,13 +1234,13 @@
         <v>1.8556</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0439</v>
+        <v>0.2201</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.963</v>
+        <v>-0.6524</v>
       </c>
       <c r="U10" t="n">
-        <v>1.0069</v>
+        <v>0.8725000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1889</v>
+        <v>-3.0799</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4848</v>
+        <v>-4.1742</v>
       </c>
       <c r="F11" t="n">
-        <v>1.296</v>
+        <v>1.0943</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3324</v>
@@ -1312,13 +1312,13 @@
         <v>0.6959</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2311</v>
+        <v>0.34</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7468</v>
+        <v>-0.4362</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9779</v>
+        <v>0.7762</v>
       </c>
       <c r="V11" t="n">
         <v>0.5361</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.76</v>
+        <v>-4.5584</v>
       </c>
       <c r="E12" t="n">
         <v>-4.5436</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2164</v>
+        <v>-0.0148</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2892</v>
@@ -1390,13 +1390,13 @@
         <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.08169999999999999</v>
+        <v>0.1199</v>
       </c>
       <c r="T12" t="n">
         <v>-0.2908</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2091</v>
+        <v>0.4107</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6778999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.554399999999999</v>
+        <v>-0.8076000000000012</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6133</v>
+        <v>-3.866499999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>3.0589</v>
+        <v>3.0587</v>
       </c>
       <c r="G13" t="n">
         <v>2.039500000000001</v>
@@ -1468,13 +1468,13 @@
         <v>12.7574</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4936</v>
+        <v>2.2404</v>
       </c>
       <c r="T13" t="n">
-        <v>-5.816400000000001</v>
+        <v>-5.0697</v>
       </c>
       <c r="U13" t="n">
-        <v>7.31</v>
+        <v>7.310100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5747</v>
+        <v>5.8657</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5877</v>
+        <v>6.3518</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0131</v>
+        <v>-0.4861</v>
       </c>
       <c r="G14" t="n">
         <v>4.2732</v>
@@ -1546,13 +1546,13 @@
         <v>2.5515</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4846</v>
+        <v>-0.1935</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7073</v>
+        <v>-0.9432</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2227</v>
+        <v>0.7497</v>
       </c>
       <c r="V14" t="n">
         <v>0.3943</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>N. WEILER-BABB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.3147</v>
+        <v>1.3515</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0031</v>
+        <v>-0.3154</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3178</v>
+        <v>1.6668</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.4807</v>
+        <v>1.5058</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.8018999999999999</v>
+        <v>-0.1103</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3212</v>
+        <v>1.6162</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.3413</v>
+        <v>2.9642</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.7695</v>
+        <v>0.6589</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4282</v>
+        <v>2.3053</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1394</v>
+        <v>-1.4583</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0323</v>
+        <v>-0.7692</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.107</v>
+        <v>-0.6891</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6959</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6959</v>
+        <v>2.3195</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0996</v>
+        <v>-0.0668</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3383</v>
+        <v>-0.8725000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.7613</v>
+        <v>0.8057</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. OSMANI</t>
+          <t>R. SMITS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3966</v>
+        <v>0.5515</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.0038</v>
+        <v>0.0431</v>
       </c>
       <c r="F16" t="n">
-        <v>1.4004</v>
+        <v>0.5083</v>
       </c>
       <c r="G16" t="n">
-        <v>-1.2974</v>
+        <v>0.6886</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.6723</v>
+        <v>-1.3793</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3748</v>
+        <v>2.0679</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7113</v>
+        <v>0.4922</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.2499</v>
+        <v>-0.6855</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5386</v>
+        <v>1.1778</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.5861</v>
+        <v>0.1963</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4223</v>
+        <v>-0.6938</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.1638</v>
+        <v>0.8901</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0876</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0883</v>
+        <v>-0.2093</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.4189</v>
+        <v>-0.3615</v>
       </c>
       <c r="U16" t="n">
-        <v>1.5072</v>
+        <v>0.1522</v>
       </c>
       <c r="V16" t="n">
-        <v>0.6778999999999999</v>
+        <v>0.5361</v>
       </c>
       <c r="W16" t="n">
-        <v>2.2862</v>
+        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.6083</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>N. WEILER-BABB</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3191</v>
+        <v>0.5405</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7872</v>
+        <v>-0.4749</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1063</v>
+        <v>1.0153</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5058</v>
+        <v>-0.4807</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1103</v>
+        <v>-0.8018999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>1.6162</v>
+        <v>0.3212</v>
       </c>
       <c r="J17" t="n">
-        <v>2.9642</v>
+        <v>-0.3413</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6589</v>
+        <v>-0.7695</v>
       </c>
       <c r="L17" t="n">
-        <v>2.3053</v>
+        <v>0.4282</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4583</v>
+        <v>-0.1394</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7692</v>
+        <v>-0.0323</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6891</v>
+        <v>-0.107</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1598</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.4793</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0991</v>
+        <v>0.3253</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3443</v>
+        <v>-0.1336</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2451</v>
+        <v>0.4589</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. DOZIER</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1348</v>
+        <v>0.2416</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7299</v>
+        <v>-0.4526</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8648</v>
+        <v>0.6942</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.1209</v>
+        <v>-0.1426</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.6796</v>
+        <v>0.396</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5587</v>
+        <v>-0.5386</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2338</v>
+        <v>0.944</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.268</v>
+        <v>0.7968</v>
       </c>
       <c r="L18" t="n">
-        <v>2.0342</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.887</v>
+        <v>-1.0866</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4116</v>
+        <v>-0.4008</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4755</v>
+        <v>-0.6859</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>2.0876</v>
       </c>
       <c r="S18" t="n">
-        <v>0.2557</v>
+        <v>-0.2368</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4086</v>
+        <v>-1.0023</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6642</v>
+        <v>0.7655</v>
       </c>
       <c r="V18" t="n">
-        <v>1.0722</v>
+        <v>-1.4665</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. SMITS</t>
+          <t>E. OSMANI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0803</v>
+        <v>0.1677</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1928</v>
+        <v>-0.8858</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2731</v>
+        <v>1.0535</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6886</v>
+        <v>-1.2974</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3793</v>
+        <v>-1.6723</v>
       </c>
       <c r="I19" t="n">
-        <v>2.0679</v>
+        <v>0.3748</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4922</v>
+        <v>-0.7113</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6855</v>
+        <v>-1.2499</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1778</v>
+        <v>0.5386</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1963</v>
+        <v>-0.5861</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6938</v>
+        <v>-0.4223</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8901</v>
+        <v>-0.1638</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6805</v>
+        <v>-0.1406</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5975</v>
+        <v>-1.301</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.083</v>
+        <v>1.1604</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5361</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0722</v>
+        <v>2.2862</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>P. DOZIER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>0.0562</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5705</v>
+        <v>-0.9659</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5705</v>
+        <v>1.022</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.1426</v>
+        <v>-2.1209</v>
       </c>
       <c r="H20" t="n">
-        <v>0.396</v>
+        <v>-2.6796</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5386</v>
+        <v>0.5587</v>
       </c>
       <c r="J20" t="n">
-        <v>0.944</v>
+        <v>-0.2338</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7968</v>
+        <v>-2.268</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1472</v>
+        <v>2.0342</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0866</v>
+        <v>-1.887</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4008</v>
+        <v>-0.4116</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6859</v>
+        <v>-1.4755</v>
       </c>
       <c r="P20" t="n">
-        <v>2.0876</v>
+        <v>0.9278</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R20" t="n">
         <v>2.0876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4784</v>
+        <v>0.177</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1202</v>
+        <v>-0.6445</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6418</v>
+        <v>0.8215</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.4665</v>
+        <v>1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3943</v>
+        <v>1.0722</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C. SWIDER</t>
+          <t>S. HAZER</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.2737</v>
+        <v>-0.1372</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.639</v>
+        <v>-0.9679</v>
       </c>
       <c r="F21" t="n">
-        <v>0.3653</v>
+        <v>0.8307</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.7726</v>
+        <v>-0.1765</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4417</v>
+        <v>0.0143</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6691</v>
+        <v>-0.1908</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.4149</v>
+        <v>0.5101</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7695</v>
+        <v>1.0657</v>
       </c>
       <c r="L21" t="n">
-        <v>0.3546</v>
+        <v>-0.5556</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3577</v>
+        <v>-0.6866</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6722</v>
+        <v>-1.0514</v>
       </c>
       <c r="O21" t="n">
-        <v>0.3145</v>
+        <v>0.3648</v>
       </c>
       <c r="P21" t="n">
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1046</v>
+        <v>0.0393</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.224</v>
+        <v>-0.3183</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3286</v>
+        <v>0.3576</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3943</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S. HAZER</t>
+          <t>C. SWIDER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6254999999999999</v>
+        <v>-0.3409</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.3218</v>
+        <v>-0.639</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6963</v>
+        <v>0.298</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.1765</v>
+        <v>-0.7726</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0143</v>
+        <v>-1.4417</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.1908</v>
+        <v>0.6691</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5101</v>
+        <v>-0.4149</v>
       </c>
       <c r="K22" t="n">
-        <v>1.0657</v>
+        <v>-0.7695</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5556</v>
+        <v>0.3546</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6866</v>
+        <v>-0.3577</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.0514</v>
+        <v>-0.6722</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3648</v>
+        <v>0.3145</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1598</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.449</v>
+        <v>0.0373</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6721</v>
+        <v>-0.224</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2232</v>
+        <v>0.2614</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.9569</v>
+        <v>-1.5631</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5092</v>
+        <v>-0.981</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.4477</v>
+        <v>-0.5822000000000001</v>
       </c>
       <c r="G23" t="n">
         <v>-1.1739</v>
@@ -2248,13 +2248,13 @@
         <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>0.9129</v>
+        <v>0.3066</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4129</v>
+        <v>-0.0589</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4999</v>
+        <v>0.3655</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4415</v>
+        <v>-1.5924</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0182</v>
+        <v>-0.9003</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4233</v>
+        <v>-0.6921</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3983</v>
@@ -2326,13 +2326,13 @@
         <v>1.1598</v>
       </c>
       <c r="S24" t="n">
-        <v>0.029</v>
+        <v>-0.1219</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7468</v>
+        <v>-0.6289</v>
       </c>
       <c r="U24" t="n">
-        <v>0.7758</v>
+        <v>0.507</v>
       </c>
       <c r="V24" t="n">
         <v>-1.0722</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.9682</v>
+        <v>-2.8002</v>
       </c>
       <c r="E25" t="n">
         <v>-2.8712</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-1.9442</v>
@@ -2404,13 +2404,13 @@
         <v>0.9278</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7921</v>
+        <v>-0.624</v>
       </c>
       <c r="T25" t="n">
         <v>-0.8215</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0294</v>
+        <v>0.1975</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,25 +2437,25 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.554400000000001</v>
+        <v>2.340900000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.059000000000001</v>
+        <v>-3.0591</v>
       </c>
       <c r="F26" t="n">
-        <v>4.613300000000001</v>
+        <v>5.3994</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.0395</v>
+        <v>-2.039499999999999</v>
       </c>
       <c r="H26" t="n">
         <v>-7.2927</v>
       </c>
       <c r="I26" t="n">
-        <v>5.253299999999999</v>
+        <v>5.253300000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>8.683399999999997</v>
+        <v>8.683400000000001</v>
       </c>
       <c r="K26" t="n">
         <v>-1.6043</v>
@@ -2482,13 +2482,13 @@
         <v>16.2369</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.4936</v>
+        <v>-0.7074</v>
       </c>
       <c r="T26" t="n">
-        <v>-7.310000000000001</v>
+        <v>-7.310200000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>5.816200000000001</v>
+        <v>6.602899999999999</v>
       </c>
       <c r="V26" t="n">
         <v>1.6083</v>
@@ -2497,7 +2497,7 @@
         <v>8.325100000000001</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.716800000000001</v>
+        <v>-6.716799999999999</v>
       </c>
     </row>
   </sheetData>
